--- a/data/employees/EMP029/AST-EMP029-06.xlsx
+++ b/data/employees/EMP029/AST-EMP029-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Drew Kim (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Drew Kim | Role: Senior Engineer | Location: Portland | Date: 2025-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>84</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP029</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+        <v>84</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>89</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP029</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>84</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP029</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>74</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>62</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>67</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>85</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>99</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>95</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>88</v>
       </c>
-      <c r="E8" t="n">
-        <v>95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>340</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>64</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>85</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>98</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>75</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>76</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>94</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>65</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp029 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>69</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP029</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP029 contributes to ast emp029 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>